--- a/sources/nina_step7.xlsx
+++ b/sources/nina_step7.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA185"/>
+  <dimension ref="A1:AB185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="76" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="102" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>ed9d2b36-c1c7-43e5-a517-f01860f2cb83</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>6152895d-f7ef-4821-a927-859e3e040522</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>fada0610-362e-403c-a667-fce3f831c312</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>a5433f07-0a80-43ec-839d-67afa4ea1edb</t>
         </is>
@@ -730,22 +736,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uf+1+2 [~5]</t>
+          <t>uf+1+2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uf+1+2 [~5]</t>
+          <t>uf+1+2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neck Throw [Tag]</t>
+          <t>Neck Throw</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neck Throw [Tag]</t>
+          <t>Neck Throw</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -790,10 +796,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>6e8f317b-fb61-46e1-bb8a-aea976243093</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0c299320-a5e4-4005-9c4e-862c5ce282ca</t>
         </is>
@@ -855,12 +866,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>40aecee0-e8e6-4a13-9922-ea239b05d89b</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>31595f70-e1dd-4834-86f7-3dc9741fa830</t>
         </is>
@@ -917,12 +928,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -931,27 +942,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2+4 [~5]; 2+5 [~5]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Swinging Toss [Tag]</t>
+          <t>Swinging Toss</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Swinging Toss [Tag]</t>
+          <t>Swinging Toss</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -979,12 +990,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1041,12 +1057,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1178,20 +1194,25 @@
       </c>
       <c r="X12" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1273,12 +1294,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>a633c26e-c550-4400-9a61-0dc7f486da39</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>26dd635f-ca93-4e51-8237-353fac7180d6</t>
         </is>
@@ -1360,12 +1381,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>857f7c66-1471-4d3a-831d-2b4a7a0200ed</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>488245e9-057e-4d48-9dfd-55031d0840ff</t>
         </is>
@@ -1447,12 +1468,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>4268837e-1fe8-4abf-b8fe-e2ea3217ce90</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0f5d75f2-c546-4d92-8ed7-06cdfe118ace</t>
         </is>
@@ -1534,12 +1555,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>b57eb5e1-f9d0-4533-8785-9b6df7842de9</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>5b21ec7a-afac-4166-ba52-e0e7c9eebb4d</t>
         </is>
@@ -1621,12 +1642,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>c7153db6-39dc-4a41-96de-8b3043b0de79</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>4b35e6fe-2c81-4ea2-8e95-28d6ae486282</t>
         </is>
@@ -1708,12 +1729,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>996f0328-89ef-4690-97d0-901635cd2f54</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>ab112ad6-8de5-46b5-a555-bf9ebd7ccda3</t>
         </is>
@@ -1795,12 +1816,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>2839d746-b9ef-4f7b-a203-62d2c85a078a</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>c508a233-bb14-4f37-a99d-2edd73fe5028</t>
         </is>
@@ -1882,12 +1903,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>ecfd81f5-9f9f-4ca9-b399-53eb281381b1</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>0664ab3e-36cb-466b-922d-5f4d3ad31084</t>
         </is>
@@ -1969,12 +1990,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>74c2b4c1-9f66-41a5-abb5-d6987c756370</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>39a23f9e-f19c-464d-b71a-76866a4a2207</t>
         </is>
@@ -2056,12 +2077,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>774d78da-3729-4c6e-9cdb-6e118b374611</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>fe6cee6b-9060-4b5d-83eb-26716b4addd5</t>
         </is>
@@ -2143,12 +2164,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>f27fc20f-73e3-4697-a3d1-46dda71220b4</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>24636200-f277-4edc-8cee-3e3441440afe</t>
         </is>
@@ -2230,12 +2251,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>991f70cf-db33-4ee0-815c-4026b1088627</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>698b1a56-b251-4266-9c3d-fb833e9f778c</t>
         </is>
@@ -2317,12 +2338,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>a6ce2b5f-0ee6-46fc-bb34-afded7428cb4</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>44d834fe-f4c7-47f8-bb84-c5b699ff2020</t>
         </is>
@@ -2404,12 +2425,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>4eb51f2c-3cea-4db7-be41-892fcd9959d9</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>77701beb-2d7a-4b54-b422-a07337a52c66</t>
         </is>
@@ -2491,12 +2512,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>1bd252ab-995c-43cc-8f0d-17c27f66cc6c</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>5c0afb7d-0044-49e4-940d-733860eb976f</t>
         </is>
@@ -2578,12 +2599,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>ebf40f0a-864c-4076-8e07-f65fd6c62c0c</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>6ed64cf0-f979-4286-98a2-232bd11013ac</t>
         </is>
@@ -2665,12 +2686,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>cd00156e-b4df-467e-bf12-7fd481a23b43</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>d9b84e75-b3d6-4a53-9934-8a9c97cf5ef4</t>
         </is>
@@ -2752,12 +2773,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>193c4651-890c-4500-b5fc-e67c62978a5e</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>f1c77965-ac5e-4a6c-96f9-c3f7ff2cc439</t>
         </is>
@@ -2839,12 +2860,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>896213c3-cb91-4612-b168-65761a283c3b</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>1bd6c3c9-22e0-4ce1-b743-7359a70e3cd0</t>
         </is>
@@ -2926,12 +2947,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>0fa4fd6d-452f-4335-b17d-98229d5b1c7f</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>0346d639-8d62-44ab-8872-e8b029d77d0b</t>
         </is>
@@ -3013,12 +3034,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>a901819e-54ca-42c1-bab2-d995dac209d9</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>a9eab50a-db8a-45c5-9024-db4c6c6ab46f</t>
         </is>
@@ -3100,12 +3121,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>b37e1ee4-9cb4-4a9c-ba9c-69a74aafd17f</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>b432395e-7ab6-4672-9414-0ec778ca0c7a</t>
         </is>
@@ -3187,12 +3208,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>e75f0ad2-a522-4c9d-a2fd-9d80789923d5</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>186a1da6-b47b-4918-a0fe-12cf3de67df3</t>
         </is>
@@ -3274,12 +3295,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>b06eb4f7-eebb-48da-9771-468478eb0823</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>8eee0560-b56d-49ba-b135-38967e59f7da</t>
         </is>
@@ -3411,20 +3432,25 @@
       </c>
       <c r="X39" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y39" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3516,12 +3542,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>970b0f63-1d70-44c1-aea1-4fffaf421a89</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>4b9e5e25-c547-4dd7-80e8-a1bbbc3db875</t>
         </is>
@@ -3613,12 +3639,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>5e6422f3-8787-4cee-be16-c4122dc0be36</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>bc3fd658-0348-4ff0-a685-b3f10fa2e414</t>
         </is>
@@ -3710,12 +3736,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>dbcb7e6a-c732-475e-9ad5-fc5b2ba05428</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>08915484-4d78-4231-b243-adf32905decf</t>
         </is>
@@ -3807,12 +3833,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>f3cd4517-f0ae-482e-ab8d-b067caedcd42</t>
         </is>
@@ -3899,17 +3925,17 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>605b7c3a-5297-45e7-a2d4-03e501546f28</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>a3f85a03-3ae4-4b56-adf1-38438e6d6d13</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -3996,17 +4022,17 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>8a38fecc-929d-419b-8520-254df58331df</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>076ca129-7df6-4efa-926b-0786f545e667</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4098,17 +4124,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>f3d9d03f-c6f2-4529-a6ac-1575a7c09279</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>8c4af992-73c8-4844-afaa-999da2bd2728</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4195,17 +4221,17 @@
           <t>hhhh</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>e1d90a9c-4b88-46da-9e3f-5fb799dc4c86</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>513635c9-6e51-4c3b-86f6-d004cb9cd563</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4292,17 +4318,17 @@
           <t>hhLh</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>1b9d438a-ec9d-4e8e-abc9-0577aea9b299</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>3a0439db-30ee-4595-8972-bf0229307e4a</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4311,22 +4337,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>– d+3,2 [~5]</t>
+          <t>– d+3,2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1,2,d+3,2 [~5]</t>
+          <t>1,2,d+3,2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>– Jail Crusher Upper - [Tag]</t>
+          <t>– Jail Crusher Upper -</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Double Punch – Jail Crusher Upper - [Tag]</t>
+          <t>Double Punch – Jail Crusher Upper -</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4396,15 +4422,20 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>d33fc0ec-e0a6-4244-a064-44f5910102ad</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>8e45c7df-bfc9-457e-bba5-9ba0a178870d</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4491,17 +4522,17 @@
           <t>hhhhm</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>c874e34f-a600-416b-b8d1-2e34b0a78642</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>c84e7a48-f2a8-4cff-b329-2eee64bd7e81</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4588,17 +4619,17 @@
           <t>hhhl</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>e5d69663-0c2a-4355-aa3b-e225bfc3ade8</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>8774be17-c10a-4fc8-96e5-079f57e251c6</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>c2820513-a15d-40ef-adc0-0bc28edbc8ec</t>
         </is>
@@ -4607,22 +4638,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>–– 2 - [~5]</t>
+          <t>–– 2 -</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1,2,3,3,2 - [~5]</t>
+          <t>1,2,3,3,2 -</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>–– Upper - [Tag]</t>
+          <t>–– Upper -</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Double Punch – Spike – Upper - [Tag]</t>
+          <t>Double Punch – Spike – Upper -</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4692,15 +4723,20 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>a1433616-ee7a-46e7-aa23-b517e41de785</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>fb56e809-c4c0-40a0-948b-37fa14c41cf3</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>e5d69663-0c2a-4355-aa3b-e225bfc3ade8</t>
         </is>
@@ -4787,17 +4823,17 @@
           <t>hhhlh</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>2b04c2d5-5240-43b9-889d-9713a9fde113</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>f72232dd-c5b1-4077-bd0d-4467e52bbb7d</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>e5d69663-0c2a-4355-aa3b-e225bfc3ade8</t>
         </is>
@@ -4884,17 +4920,17 @@
           <t>hhhlL</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>b94dfb6e-6b02-46ca-a0a7-8fdc2d9cd8e0</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>9d8aca87-2f9e-4e55-a29a-a9e784c27067</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>e5d69663-0c2a-4355-aa3b-e225bfc3ade8</t>
         </is>
@@ -4991,12 +5027,12 @@
           <t>CF</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>48d36ecb-aef9-486c-b683-93ed185e3929</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>6a324267-0268-4d7f-b29a-6cafa7e57ee8</t>
         </is>
@@ -5088,12 +5124,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>1bd159f3-36ea-4b47-b9ee-55b2edb449d3</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>89750ca1-4348-43f7-a620-38bf67a9c170</t>
         </is>
@@ -5190,12 +5226,12 @@
           <t>OS</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>ac07999e-e8f3-4515-8907-2d6bb8250738</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>48394692-c558-4be9-a75d-2501231d766b</t>
         </is>
@@ -5287,12 +5323,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>795b3e16-b5db-4336-a531-dddf1c5c7a80</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>fc8a1641-b54f-446f-abaf-0bed255e29b0</t>
         </is>
@@ -5364,17 +5400,17 @@
           <t>m-</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>e95ede68-7ad9-4249-bfe1-b6e7f2bacc31</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>27695ff6-c922-49d4-98e4-495334d3e7a7</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>795b3e16-b5db-4336-a531-dddf1c5c7a80</t>
         </is>
@@ -5451,17 +5487,17 @@
           <t>Continue with the corresponding Multi Throw extentions.</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>154bc9e2-1a30-4038-93f7-603bc28dd32f</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>5c34689e-f3b2-446b-99cb-4607e436c93c</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>e95ede68-7ad9-4249-bfe1-b6e7f2bacc31</t>
         </is>
@@ -5538,17 +5574,17 @@
           <t>MS DSc</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>1630095d-98f4-4ffc-acae-1d188474b20d</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>41346071-a0f3-4f02-a067-73da24fa0401</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>e95ede68-7ad9-4249-bfe1-b6e7f2bacc31</t>
         </is>
@@ -5620,17 +5656,17 @@
           <t>m-M</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>69b47516-016b-4e0d-b9c0-2f5b48b601a8</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>6970abc3-72cd-4343-8357-cc79b4930b00</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>e95ede68-7ad9-4249-bfe1-b6e7f2bacc31</t>
         </is>
@@ -5697,17 +5733,17 @@
           <t>m-</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>b6f7b636-4526-4335-94c3-8481023dc703</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>07af1e25-c0fa-4ae8-bd14-eabd56a8a6e0</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>e95ede68-7ad9-4249-bfe1-b6e7f2bacc31</t>
         </is>
@@ -5779,17 +5815,17 @@
           <t>m-</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>d03a4da5-baad-42e5-b961-41a791c5acde</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>c3a450db-a82a-48f9-9895-51c101cefb99</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>795b3e16-b5db-4336-a531-dddf1c5c7a80</t>
         </is>
@@ -5866,17 +5902,17 @@
           <t>Continue with the corresponding Multi Throw extentions.</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>f1d0faa3-2764-4077-b54f-0d1782a01a1a</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>b366671b-f3a4-4f7b-bacf-836470e90ef7</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>d03a4da5-baad-42e5-b961-41a791c5acde</t>
         </is>
@@ -5968,12 +6004,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>ca9b666d-24a1-4490-83c6-1a9ca84e4506</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>81754af7-95c9-44ef-bea7-b36bbc6432e0</t>
         </is>
@@ -6065,12 +6101,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>234aa141-0c72-4b37-a8c2-ea7ef80b1bf9</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>d3586c29-7da1-4c76-9cef-24908710ace8</t>
         </is>
@@ -6167,12 +6203,12 @@
           <t>MS FScco</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>3eea4eff-4a36-4a69-878a-012441c4a8a8</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>5911c260-b1fa-45fb-a4d6-9ae311ba5e78</t>
         </is>
@@ -6269,12 +6305,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>2f476f61-7707-490e-a9ed-4e465c4e23bb</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>3bb5ea20-dd4a-473e-b49e-b82b8a525460</t>
         </is>
@@ -6366,12 +6402,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>973ff651-1e20-4fc9-8850-e59f157487e0</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>d6e7eaca-689a-4271-b957-64faab3b2640</t>
         </is>
@@ -6468,12 +6504,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>01647bf0-e635-4aaa-954a-ae93ef49ddb1</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>9ae63eb3-8d1d-4a17-8e7d-1fb9eee90d0e</t>
         </is>
@@ -6565,12 +6601,12 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>98de3df5-8508-4cd5-b1c8-f683c2a67b98</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>3a5f7582-cbc1-44ff-8dfb-326c2eafc41c</t>
         </is>
@@ -6662,12 +6698,12 @@
           <t>hhL</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>df5c15c4-f158-4446-80d3-8da02860e2f2</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>0aeb4dd9-42d9-4b8d-b59b-dde29e21abca</t>
         </is>
@@ -6676,22 +6712,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>– 2 - [~5]</t>
+          <t>– 2 -</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2,3,3,2 - [~5]</t>
+          <t>2,3,3,2 -</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>– Upper - [Tag]</t>
+          <t>– Upper -</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jab - Spike Combo – Upper - [Tag]</t>
+          <t>Jab - Spike Combo – Upper -</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6756,15 +6792,20 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
           <t>6ec78850-8f80-43c5-b79b-eee3f04fc9ff</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>750e21b3-7d5c-40bb-adfc-088f7fcefb72</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>df5c15c4-f158-4446-80d3-8da02860e2f2</t>
         </is>
@@ -6851,17 +6892,17 @@
           <t>hhLh</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>33796847-2646-4bfe-839e-4c4106454160</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>8255e74b-7f38-4ced-b07e-ae050e1d55b4</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>df5c15c4-f158-4446-80d3-8da02860e2f2</t>
         </is>
@@ -6948,17 +6989,17 @@
           <t>hhLL</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>f5706255-c71e-4b8b-873e-8e2bcafa30d1</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>ced70998-1efb-4e27-8ebd-daafee174ccb</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>df5c15c4-f158-4446-80d3-8da02860e2f2</t>
         </is>
@@ -6967,22 +7008,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2,d+3,2 [~5]</t>
+          <t>2,d+3,2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2,d+3,2 [~5]</t>
+          <t>2,d+3,2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jab - Jail Crucher Upper - [Tag]</t>
+          <t>Jab - Jail Crucher Upper -</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jab - Jail Crucher Upper - [Tag]</t>
+          <t>Jab - Jail Crucher Upper -</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7057,10 +7098,15 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>60612653-419b-4e05-9ef3-b03930a1e46d</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>17fd13ee-d523-44ab-8433-52c70de1f327</t>
         </is>
@@ -7152,12 +7198,12 @@
           <t>hLh</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>ea69615a-2264-488e-84bc-fba5ea10d410</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>fe79856e-40b7-448b-acb2-838cd512b649</t>
         </is>
@@ -7249,12 +7295,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>10937154-49f5-423e-a724-78dafc62e5ac</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>16d357a3-d607-41f3-aca5-9c93651a9235</t>
         </is>
@@ -7311,12 +7357,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>8ddc3dbf-8948-4dae-a5c8-502aa93bdb22</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>c9435685-bed6-490e-9c41-c2047394954d</t>
         </is>
@@ -7413,12 +7459,12 @@
           <t>Female opponents can slap reverse Nina with 2 Nina can slap again with 2..</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>3501251f-f796-40ba-a6fa-04b6be7bb61c</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>604f83f6-dfea-4478-9cbe-d55fadff06f8</t>
         </is>
@@ -7515,12 +7561,12 @@
           <t>FS</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>c6e65bef-8598-4cad-97e7-a4c6d112251b</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>91c4d662-95b5-46eb-83a0-3d9a22e94497</t>
         </is>
@@ -7617,12 +7663,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>a4215110-df0b-4ab6-8d79-05d7c3f681b9</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>bc0c34e3-8353-44e7-907f-cac203a49b17</t>
         </is>
@@ -7719,12 +7765,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>a8f2dfba-eeea-4289-9705-9fbf7a204ffb</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>f74f8469-2ac3-4f35-880b-61a26c0d7dfd</t>
         </is>
@@ -7821,12 +7867,12 @@
           <t>GB JGc</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>ffb4f4a4-8a87-4303-9f77-e51b2e7994ef</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>00babf63-5ebd-4f8d-b34c-805417cb7d69</t>
         </is>
@@ -7835,22 +7881,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>d,df+2 [~5]</t>
+          <t>d,df+2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>d,df+2 [~5]</t>
+          <t>d,df+2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Shut Up [Tag]</t>
+          <t>Shut Up</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shut Up [Tag]</t>
+          <t>Shut Up</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7925,10 +7971,15 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
           <t>04bb01ab-3e2d-4b3b-88ca-65086731b59e</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>ffbdbe4b-94b7-4557-b93a-43c4eb525706</t>
         </is>
@@ -8020,12 +8071,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>1f0d8a6e-6012-4204-aaa9-75a5e2b7e668</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>c61ff655-131f-4275-8c1d-6399d4188690</t>
         </is>
@@ -8127,12 +8178,12 @@
           <t>MS DSc</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>f7b83299-0cd6-4b6e-9b9e-f0252468ea5a</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>42cbef19-4be1-436a-8d5f-1dc4425b4b53</t>
         </is>
@@ -8229,12 +8280,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>25378d95-1d91-4a21-b1ad-c1c8f0e8050b</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>3b132157-7924-4fc5-949f-e22ad0db6afb</t>
         </is>
@@ -8326,12 +8377,12 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>f8743701-60b8-4ba1-a65b-53308ca9a781</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>259474fb-153c-46c8-9842-209ff8801812</t>
         </is>
@@ -8340,22 +8391,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>– 2 - [~5]</t>
+          <t>– 2 -</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3,3,2 - [~5]</t>
+          <t>3,3,2 -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>– Upper - [Tag]</t>
+          <t>– Upper -</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Spike Combo – Upper - [Tag]</t>
+          <t>Spike Combo – Upper -</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8425,15 +8476,20 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
           <t>7340c784-779b-49c0-a240-ee9192a47da7</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>1ae7353c-8435-407d-bd4c-52c867a913c2</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>f8743701-60b8-4ba1-a65b-53308ca9a781</t>
         </is>
@@ -8510,17 +8566,17 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>9af56650-abb5-4e3e-8508-1a1edae6d7c2</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>e6677ed6-a39c-439d-a82c-e31e80cc7b55</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>f8743701-60b8-4ba1-a65b-53308ca9a781</t>
         </is>
@@ -8607,17 +8663,17 @@
           <t>hlh</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>bd5dc8fc-049b-4866-b747-8c5f2c769653</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>3eca6a18-57e6-49b4-8a4c-d4ec6f67aa19</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>f8743701-60b8-4ba1-a65b-53308ca9a781</t>
         </is>
@@ -8704,17 +8760,17 @@
           <t>hlL</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>db5396b4-a560-4ce3-a29b-66b6c84da143</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>5388e103-7e5a-4f4b-90db-4f089049e6fd</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>f8743701-60b8-4ba1-a65b-53308ca9a781</t>
         </is>
@@ -8723,27 +8779,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FC+3,2 [~5]</t>
+          <t>FC+3,2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FC+3,2 [~5]</t>
+          <t>FC+3,2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>d+3,2 [~5]</t>
+          <t>d+3,2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Low Spin Kick - Upper - [Tag]</t>
+          <t>Low Spin Kick - Upper -</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Low Spin Kick - Upper - [Tag]</t>
+          <t>Low Spin Kick - Upper -</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8818,10 +8874,15 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>b8aa9dd1-714f-430d-9fac-456e7b4b0789</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>4abdfa3e-1ad2-4d38-b987-5183d50ec15c</t>
         </is>
@@ -8918,12 +8979,12 @@
           <t>Lh</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>199bc558-9abe-4410-85c6-675aa57615fd</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>a83a08d8-ce8b-40ea-9758-3fe6ac3ea087</t>
         </is>
@@ -9020,12 +9081,12 @@
           <t>Ll</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>15d4ea85-f232-4b80-940d-019277ebbc08</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>6ad0b522-0349-4ad1-9716-52a654ac5486</t>
         </is>
@@ -9034,27 +9095,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>uf,N,d+3,2 [~5]</t>
+          <t>uf,N,d+3,2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>uf,N,d+3,2 [~5]</t>
+          <t>uf,N,d+3,2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>uf,N,db+3,2 [~5]; uf,N,df+3,2 [~5]</t>
+          <t>uf,N,db+3,2; uf,N,df+3,2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Hop - Low Spin Kick - Upper - [Tag]</t>
+          <t>Hop - Low Spin Kick - Upper -</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hop - Low Spin Kick - Upper - [Tag]</t>
+          <t>Hop - Low Spin Kick - Upper -</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9129,10 +9190,15 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>d653b923-c8b2-4a9a-9191-03ef8d82daef</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>4df714d6-52c9-44c6-a90c-854bbba6efb3</t>
         </is>
@@ -9229,12 +9295,12 @@
           <t>Lm</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>2ff94016-1ad4-4b21-903b-55e482cb3b26</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>d669c416-1fbb-46ea-a275-7229dc332bbf</t>
         </is>
@@ -9331,12 +9397,12 @@
           <t>Lh</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>169f3583-cc03-4385-b22c-3027eac84adf</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>4222c5b6-1b19-4ceb-9afd-cc8fb75db6d6</t>
         </is>
@@ -9433,12 +9499,12 @@
           <t>Nina can link into SS+2 from this SS cancel, but not the other SS moves.</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>4ad00c0b-a5ca-4740-b004-d845f33b00c1</t>
         </is>
@@ -9525,17 +9591,17 @@
           <t>mhh</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>d1dcf324-06c9-4b37-b06c-f2a4104b6bbe</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>7f6de3b1-c8c7-44c9-baa9-4dd4eb71c8fe</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
@@ -9627,17 +9693,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>8e10dfe6-d45b-4fc8-af90-81fa177cfa09</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>274192cb-89d1-4cb4-ac8e-90b0cb1638c4</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
@@ -9646,22 +9712,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>–– 2 [~5]</t>
+          <t>–– 2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3,2 [~5]</t>
+          <t>df+3,2 [~U_~D],d+3,2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>–– Upper [Tag]</t>
+          <t>–– Upper</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – Upper [Tag]</t>
+          <t>Creeping Snake [Side Step] – Low Spin Kick – Upper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9731,15 +9797,20 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
           <t>1d22fc29-9d90-4e34-9628-9ae195aa9c12</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>93bc1d5e-be0a-49db-a492-bae3eeb97bcb</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>8e10dfe6-d45b-4fc8-af90-81fa177cfa09</t>
         </is>
@@ -9826,17 +9897,17 @@
           <t>mhLh</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>7cd14d34-a831-4d9d-86cd-272b84598784</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>e8432875-5104-4377-98af-f85c44b1c979</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>8e10dfe6-d45b-4fc8-af90-81fa177cfa09</t>
         </is>
@@ -9923,17 +9994,17 @@
           <t>mhhl</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>3dc16b20-fee0-48d1-a6c8-6f6160bb796e</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>6ebd8473-cac8-406e-80ef-95c9e4ba1154</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
@@ -9942,22 +10013,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>–– 2 [~5]</t>
+          <t>–– 2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,2 [~5]</t>
+          <t>df+3,2 [~U_~D],3,3,2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>–– Upper [Tag]</t>
+          <t>–– Upper</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Upper [Tag]</t>
+          <t>Creeping Snake [Side Step] – Spike Combo – Upper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10027,15 +10098,20 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
           <t>f8008efd-1530-4147-959a-e3bc642b5d40</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>ba8e5554-ef54-4997-a0e9-6289c23959c8</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>3dc16b20-fee0-48d1-a6c8-6f6160bb796e</t>
         </is>
@@ -10122,17 +10198,17 @@
           <t>mhhlh</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>f11adc9e-0d02-48fe-84a6-7e1fe90d5b70</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>c9186766-b394-40c4-b75f-724080d52b42</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
+      <c r="AA108" t="inlineStr">
         <is>
           <t>3dc16b20-fee0-48d1-a6c8-6f6160bb796e</t>
         </is>
@@ -10219,17 +10295,17 @@
           <t>mhhlL</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>c4a04a83-def2-4c5c-a855-0d12c4ad842a</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>ac3a8c47-2732-4aad-8936-85f9f56d0ade</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
+      <c r="AA109" t="inlineStr">
         <is>
           <t>3dc16b20-fee0-48d1-a6c8-6f6160bb796e</t>
         </is>
@@ -10316,17 +10392,17 @@
           <t>mhhh</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>7b0c4542-5199-4a91-8356-f4cc01aec649</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>3e2c23cd-3735-46d0-9f9f-0e6ed38e5c14</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
@@ -10413,17 +10489,17 @@
           <t>mhhL</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>476e3e63-d7c7-4323-92c9-2426f9036126</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>893ab699-7816-4415-83fb-9078ba371f60</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>a4a3c8ec-6ede-43b4-82a0-c27c0bed2c9a</t>
         </is>
@@ -10515,12 +10591,12 @@
           <t>mhhm</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>d4829f9c-207a-474c-946c-431cc51ef854</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>fe997a39-59b9-4cfc-9f64-8b602f1543ad</t>
         </is>
@@ -10612,12 +10688,12 @@
           <t>mhh</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>efabb8b9-bef7-42ab-965f-2f1d4b56f944</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>bbed0fb1-b9de-4dd7-8b6f-8f064a15c5f4</t>
         </is>
@@ -10704,17 +10780,17 @@
           <t>mhhl</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>59132de2-c101-4332-b8e7-664c3bc7cf6f</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>ce18108b-b88f-4954-8031-eb128bb2f18b</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>efabb8b9-bef7-42ab-965f-2f1d4b56f944</t>
         </is>
@@ -10801,17 +10877,17 @@
           <t>mhhh</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>373f2c5c-7d73-49e0-b4e3-4239b31909d2</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>4e1bf9a8-860c-4675-a95b-3ad395df6938</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
+      <c r="AA115" t="inlineStr">
         <is>
           <t>efabb8b9-bef7-42ab-965f-2f1d4b56f944</t>
         </is>
@@ -10898,17 +10974,17 @@
           <t>mhhhhm</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>8ba9ede4-7f72-4516-ae42-31079b68bcf9</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>d2329c89-ca1f-47bf-a543-6c6745ce41cb</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
+      <c r="AA116" t="inlineStr">
         <is>
           <t>efabb8b9-bef7-42ab-965f-2f1d4b56f944</t>
         </is>
@@ -11000,12 +11076,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>4c500ceb-d882-449d-b58b-3ecfcca62943</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>939bcf4e-8ee0-4901-86fc-9a3c4f3df1a8</t>
         </is>
@@ -11014,27 +11090,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>d,db+3 [~5]</t>
+          <t>d,db+3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>d,db+3 [~5]</t>
+          <t>d,db+3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>db+3+4 [~5]</t>
+          <t>db+3+4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Divine Cannon [Tag]</t>
+          <t>Divine Cannon</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Divine Cannon [Tag]</t>
+          <t>Divine Cannon</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -11109,10 +11185,15 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
           <t>f41995f3-8f78-4c77-a8e8-e7859a1163ff</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>3ae18fef-deb5-4077-8e4b-e0f747ad4ff0</t>
         </is>
@@ -11214,12 +11295,12 @@
           <t>Move can only be done when the opponent is knocked of his feet.</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>3b3b6a72-357c-448d-becd-aee2fada9a2b</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>b4e645a0-b7f4-4ee7-ac33-a677145cbf5e</t>
         </is>
@@ -11316,12 +11397,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>faff646e-3bff-43e1-95b8-59f02533009b</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>168e543d-8d44-4924-b226-ad199efb6908</t>
         </is>
@@ -11398,17 +11479,17 @@
           <t>Continue with the corresponding Multi Throw extentions.</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>6cfef457-5cce-4d18-9b06-be51bef7e5e7</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>5f868945-f9cb-485c-a04c-03263b4ac10b</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
+      <c r="AA121" t="inlineStr">
         <is>
           <t>faff646e-3bff-43e1-95b8-59f02533009b</t>
         </is>
@@ -11505,12 +11586,12 @@
           <t>BS KS</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>e63e0b52-8b80-4832-a239-a0bee2e611a9</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>72a33a04-da14-4199-835f-b693ea074d8b</t>
         </is>
@@ -11577,12 +11658,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="Y123" t="inlineStr">
         <is>
           <t>b4fc8b18-8276-4dec-bbd2-e2556eb76745</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>0524a72e-99b2-4e4b-bf4c-582577f1d7db</t>
         </is>
@@ -11679,12 +11760,12 @@
           <t>BS RC</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>5576d85a-5003-4acc-bb54-1cb664bd3834</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>6d597bd8-15be-49cd-902a-312c48538e01</t>
         </is>
@@ -11786,12 +11867,12 @@
           <t>Nina can link into SS+2 from this SS cancel, but not the other SS moves.</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>b982dec9-a4af-40d1-9ef2-a3c1d22aa0bf</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>7995be6e-d266-400c-9027-2a2143ec3929</t>
         </is>
@@ -11883,12 +11964,12 @@
           <t>hL</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>f2e72893-48c1-48c1-ab22-9772a294e0d4</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>28f9dc68-33fe-443b-b666-ce53530a4f6a</t>
         </is>
@@ -11897,22 +11978,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>– 2 - [~5]</t>
+          <t>– 2 -</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4,3,2 - [~5]</t>
+          <t>4,3,2 -</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>– Upper - [Tag]</t>
+          <t>– Upper -</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Blonde Attack – Upper - [Tag]</t>
+          <t>Blonde Attack – Upper -</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11982,15 +12063,20 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
           <t>8b1ea8fb-5633-49a5-b52a-4f1ac284c04a</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>b294ff69-1cac-46c9-a2fc-5f616c6dde4d</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>f2e72893-48c1-48c1-ab22-9772a294e0d4</t>
         </is>
@@ -12077,17 +12163,17 @@
           <t>hLh</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>5fba3538-d23e-4c7e-924a-4cb9737b7f8c</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>573f6698-ec2e-4a29-ae46-8ce363793aef</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>f2e72893-48c1-48c1-ab22-9772a294e0d4</t>
         </is>
@@ -12174,17 +12260,17 @@
           <t>hLL</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>a5b4a0a4-8239-49f9-8bf5-c8dde40b4e37</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>407d3dac-0206-41a3-9cc1-c969399cb486</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
+      <c r="AA129" t="inlineStr">
         <is>
           <t>f2e72893-48c1-48c1-ab22-9772a294e0d4</t>
         </is>
@@ -12276,12 +12362,12 @@
           <t>hlh</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>cf9d954d-1664-49c7-9636-45c4a47f8310</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>75c5ce42-b37e-40d1-91b3-5d634ccf891a</t>
         </is>
@@ -12333,12 +12419,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>ccc8325c-31d4-40a1-b5ae-578775158595</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>f209eaa2-dc44-43a0-a86d-452b05ae9107</t>
         </is>
@@ -12347,22 +12433,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>db+4,3 [~5]</t>
+          <t>db+4,3</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>db+4,3 [~5]</t>
+          <t>db+4,3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Slicer - Divine Cannon [Tag]</t>
+          <t>Slicer - Divine Cannon</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Slicer - Divine Cannon [Tag]</t>
+          <t>Slicer - Divine Cannon</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -12437,10 +12523,15 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
           <t>07f3a020-9dc7-4fef-8764-f15e900e748d</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>b3f3b43c-afc3-44a7-a8c8-3b678a83a7f8</t>
         </is>
@@ -12497,12 +12588,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X133" t="inlineStr">
+      <c r="Y133" t="inlineStr">
         <is>
           <t>3803a453-0a5b-49e0-ac21-6e19056b5457</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>69017d65-c44e-4120-a9e7-07cfef853157</t>
         </is>
@@ -12559,12 +12650,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>13a16837-f29b-497a-9891-dd861814494d</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>4846b486-f1b7-4892-992b-b0f4b128c747</t>
         </is>
@@ -12616,12 +12707,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
+      <c r="Y135" t="inlineStr">
         <is>
           <t>e07544e9-9d9d-4bed-bfac-7e83ea08081b</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>34ee227e-65ea-42bf-8752-32616b40a88f</t>
         </is>
@@ -12753,20 +12844,25 @@
       </c>
       <c r="X138" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y138" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y138" s="1" t="inlineStr">
+      <c r="Z138" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z138" s="1" t="inlineStr">
+      <c r="AA138" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA138" s="1" t="inlineStr">
+      <c r="AB138" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -12848,12 +12944,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>3f312a21-8392-496d-96d2-8902645f69cd</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>2e3110a2-185d-44c0-a2f7-f0c819d8cc51</t>
         </is>
@@ -12920,17 +13016,17 @@
           <t>!-</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr">
+      <c r="Y140" t="inlineStr">
         <is>
           <t>c8c308a1-8968-42c3-a3cf-f43fa73b64fc</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>e50320b1-7104-4292-a4e9-afbb3e263c1d</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
+      <c r="AA140" t="inlineStr">
         <is>
           <t>3f312a21-8392-496d-96d2-8902645f69cd</t>
         </is>
@@ -13002,12 +13098,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="Y141" t="inlineStr">
         <is>
           <t>39090d6b-735a-40fc-87e2-2839e1bc184f</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>5c784d8c-75a8-4c21-b079-61f2010d701f</t>
         </is>
@@ -13139,20 +13235,25 @@
       </c>
       <c r="X144" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y144" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y144" s="1" t="inlineStr">
+      <c r="Z144" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z144" s="1" t="inlineStr">
+      <c r="AA144" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA144" s="1" t="inlineStr">
+      <c r="AB144" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -13161,22 +13262,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5]</t>
+          <t>qcf+1+2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5]</t>
+          <t>qcf+1+2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag]</t>
+          <t>Palm Strike</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag]</t>
+          <t>Palm Strike</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -13209,12 +13310,17 @@
           <t>Special Tag Throw with Anna only. Anna finishes with a Reverse Shoulder Lock. Total damage is 15,30.</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
         </is>
       </c>
-      <c r="AA145" t="inlineStr">
+      <c r="AB145" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13228,7 +13334,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],3,4,3,1+2</t>
+          <t>qcf+1+2,3,4,3,1+2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -13238,7 +13344,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Arm Bar</t>
+          <t>Palm Strike – Arm Bar</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -13261,17 +13367,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Z146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
+      <c r="AA146" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr">
+      <c r="AB146" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13285,7 +13391,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],2,3,4,2,2</t>
+          <t>qcf+1+2,2,3,4,2,2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -13295,7 +13401,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Double Snap</t>
+          <t>Palm Strike – Double Snap</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -13318,17 +13424,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Z147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
+      <c r="AA147" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
+      <c r="AB147" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13342,7 +13448,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],2,3,4,2,2,1,3+4,1,2,1+2</t>
+          <t>qcf+1+2,2,3,4,2,2,1,3+4,1,2,1+2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13352,7 +13458,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Double Snap – Neck Crusher</t>
+          <t>Palm Strike – Double Snap – Neck Crusher</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -13375,17 +13481,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
+      <c r="AA148" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
         </is>
       </c>
-      <c r="AA148" t="inlineStr">
+      <c r="AB148" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13399,7 +13505,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],2,3,4,2,2,1,2,4,3,1+2+3</t>
+          <t>qcf+1+2,2,3,4,2,2,1,2,4,3,1+2+3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13409,7 +13515,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Double Snap – Gale Tech Strech</t>
+          <t>Palm Strike – Double Snap – Gale Tech Strech</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -13432,17 +13538,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
+      <c r="AA149" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
+      <c r="AB149" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13456,7 +13562,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1</t>
+          <t>qcf+1+2,1,3,2,1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13466,7 +13572,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock</t>
+          <t>Palm Strike – Standing Reverse Arm Lock</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -13489,17 +13595,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Z150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
+      <c r="AA150" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
+      <c r="AB150" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13513,7 +13619,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1,3,1,4,1+2,1+2</t>
+          <t>qcf+1+2,1,3,2,1,3,1,4,1+2,1+2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13523,7 +13629,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock – Rear Gale Tech Falcon Wing</t>
+          <t>Palm Strike – Standing Reverse Arm Lock – Rear Gale Tech Falcon Wing</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -13546,17 +13652,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr">
+      <c r="AB151" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13570,7 +13676,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1,2,1,3,4,1+2</t>
+          <t>qcf+1+2,1,3,2,1,2,1,3,4,1+2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13580,7 +13686,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock – Falling Reverse Arm Lock</t>
+          <t>Palm Strike – Standing Reverse Arm Lock – Falling Reverse Arm Lock</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13603,17 +13709,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="Z152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
+      <c r="AA152" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
         </is>
       </c>
-      <c r="AA152" t="inlineStr">
+      <c r="AB152" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13665,12 +13771,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr">
+      <c r="AB153" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13722,17 +13828,17 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="Z154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
+      <c r="AA154" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr">
+      <c r="AB154" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13779,17 +13885,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
+      <c r="AA155" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
+      <c r="AB155" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13846,12 +13952,12 @@
           <t>CH</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
+      <c r="Z156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
         </is>
       </c>
-      <c r="AA156" t="inlineStr">
+      <c r="AB156" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13898,17 +14004,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
+      <c r="Z157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
+      <c r="AA157" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
         </is>
       </c>
-      <c r="AA157" t="inlineStr">
+      <c r="AB157" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13955,17 +14061,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="Z158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
+      <c r="AA158" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
+      <c r="AB158" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14017,12 +14123,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="Z159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
         </is>
       </c>
-      <c r="AA159" t="inlineStr">
+      <c r="AB159" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14069,17 +14175,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="Z160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
+      <c r="AA160" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
+      <c r="AB160" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14126,17 +14232,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
+      <c r="Z161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
+      <c r="AA161" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
         </is>
       </c>
-      <c r="AA161" t="inlineStr">
+      <c r="AB161" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14183,17 +14289,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
+      <c r="Z162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
+      <c r="AA162" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
         </is>
       </c>
-      <c r="AA162" t="inlineStr">
+      <c r="AB162" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14240,17 +14346,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y163" t="inlineStr">
+      <c r="Z163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
+      <c r="AA163" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
         </is>
       </c>
-      <c r="AA163" t="inlineStr">
+      <c r="AB163" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14297,12 +14403,12 @@
           <t>Front</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="Z164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
         </is>
       </c>
-      <c r="AA164" t="inlineStr">
+      <c r="AB164" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14349,17 +14455,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
+      <c r="Z165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
+      <c r="AA165" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
         </is>
       </c>
-      <c r="AA165" t="inlineStr">
+      <c r="AB165" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14406,17 +14512,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="Z166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
+      <c r="AA166" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
         </is>
       </c>
-      <c r="AA166" t="inlineStr">
+      <c r="AB166" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14463,17 +14569,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="Z167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
+      <c r="AA167" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
         </is>
       </c>
-      <c r="AA167" t="inlineStr">
+      <c r="AB167" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14520,17 +14626,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr">
+      <c r="Z168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
+      <c r="AA168" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
+      <c r="AB168" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14577,17 +14683,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
+      <c r="Z169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
+      <c r="AA169" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
         </is>
       </c>
-      <c r="AA169" t="inlineStr">
+      <c r="AB169" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14634,17 +14740,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="Z170" t="inlineStr">
         <is>
           <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
+      <c r="AA170" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
         </is>
       </c>
-      <c r="AA170" t="inlineStr">
+      <c r="AB170" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14776,20 +14882,25 @@
       </c>
       <c r="X173" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y173" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y173" s="1" t="inlineStr">
+      <c r="Z173" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z173" s="1" t="inlineStr">
+      <c r="AA173" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA173" s="1" t="inlineStr">
+      <c r="AB173" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -14831,12 +14942,12 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
-      <c r="Y174" t="inlineStr">
+      <c r="Z174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
         </is>
       </c>
-      <c r="AA174" t="inlineStr">
+      <c r="AB174" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14878,12 +14989,12 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
-      <c r="Y175" t="inlineStr">
+      <c r="Z175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
         </is>
       </c>
-      <c r="AA175" t="inlineStr">
+      <c r="AB175" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14925,12 +15036,12 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
-      <c r="Y176" t="inlineStr">
+      <c r="Z176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
         </is>
       </c>
-      <c r="AA176" t="inlineStr">
+      <c r="AB176" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -14972,12 +15083,12 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
-      <c r="Y177" t="inlineStr">
+      <c r="Z177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
         </is>
       </c>
-      <c r="AA177" t="inlineStr">
+      <c r="AB177" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15019,12 +15130,12 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
-      <c r="Y178" t="inlineStr">
+      <c r="Z178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
         </is>
       </c>
-      <c r="AA178" t="inlineStr">
+      <c r="AB178" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15066,12 +15177,12 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr">
+      <c r="Z179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
         </is>
       </c>
-      <c r="AA179" t="inlineStr">
+      <c r="AB179" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15113,12 +15224,12 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
-      <c r="Y180" t="inlineStr">
+      <c r="Z180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr">
+      <c r="AB180" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15160,12 +15271,12 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
-      <c r="Y181" t="inlineStr">
+      <c r="Z181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
         </is>
       </c>
-      <c r="AA181" t="inlineStr">
+      <c r="AB181" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15207,12 +15318,12 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
-      <c r="Y182" t="inlineStr">
+      <c r="Z182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
         </is>
       </c>
-      <c r="AA182" t="inlineStr">
+      <c r="AB182" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15259,12 +15370,12 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
-      <c r="Y183" t="inlineStr">
+      <c r="Z183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
         </is>
       </c>
-      <c r="AA183" t="inlineStr">
+      <c r="AB183" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15311,12 +15422,12 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
-      <c r="Y184" t="inlineStr">
+      <c r="Z184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr">
+      <c r="AB184" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -15363,12 +15474,12 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
-      <c r="Y185" t="inlineStr">
+      <c r="Z185" t="inlineStr">
         <is>
           <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr">
+      <c r="AB185" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/nina_step7.xlsx
+++ b/sources/nina_step7.xlsx
@@ -423,9 +423,9 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -9411,22 +9411,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9518,7 +9523,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]&lt;4</t>
+          <t>df+3,2&lt;4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9528,7 +9533,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9615,7 +9620,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3</t>
+          <t>df+3,2,d+3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9625,7 +9630,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick</t>
+          <t>Creeping Snake – Low Spin Kick</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9717,7 +9722,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3,2</t>
+          <t>df+3,2,d+3,2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9727,7 +9732,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – Upper</t>
+          <t>Creeping Snake – Low Spin Kick – Upper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9824,7 +9829,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3,4</t>
+          <t>df+3,2,d+3,4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9834,7 +9839,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – High Kick</t>
+          <t>Creeping Snake – Low Spin Kick – High Kick</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9921,7 +9926,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3</t>
+          <t>df+3,2,3,3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9931,7 +9936,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo</t>
+          <t>Creeping Snake – Spike Combo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10018,7 +10023,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,2</t>
+          <t>df+3,2,3,3,2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -10028,7 +10033,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Upper</t>
+          <t>Creeping Snake – Spike Combo – Upper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10125,7 +10130,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,4</t>
+          <t>df+3,2,3,3,4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -10135,7 +10140,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – High Kick</t>
+          <t>Creeping Snake – Spike Combo – High Kick</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10222,7 +10227,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3,3,d+4</t>
+          <t>df+3,2,3,3,d+4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -10232,7 +10237,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Shin Kick</t>
+          <t>Creeping Snake – Spike Combo – Shin Kick</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10319,7 +10324,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3&lt;4</t>
+          <t>df+3,2,3&lt;4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10329,7 +10334,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Head Ringer</t>
+          <t>Creeping Snake – Head Ringer</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10416,7 +10421,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],1&lt;4</t>
+          <t>df+3,2,1&lt;4</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -10426,7 +10431,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11774,27 +11779,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>d+4,1 [~U_~D]</t>
+          <t>d+4,1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">

--- a/sources/nina_step7.xlsx
+++ b/sources/nina_step7.xlsx
@@ -928,6 +928,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
@@ -995,6 +1000,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
@@ -1055,6 +1065,11 @@
       <c r="U9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -13325,6 +13340,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
+        </is>
+      </c>
       <c r="Z145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
@@ -13377,6 +13397,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
+        </is>
+      </c>
       <c r="Z146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -13434,6 +13459,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
+        </is>
+      </c>
       <c r="Z147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -13491,6 +13521,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
+        </is>
+      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -13548,6 +13583,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -13605,6 +13645,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
+        </is>
+      </c>
       <c r="Z150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -13662,6 +13707,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
+        </is>
+      </c>
       <c r="Z151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -13719,6 +13769,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
+        </is>
+      </c>
       <c r="Z152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
@@ -13781,6 +13836,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
+        </is>
+      </c>
       <c r="Z153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
@@ -13838,6 +13898,11 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
+        </is>
+      </c>
       <c r="Z154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
@@ -13895,6 +13960,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
+        </is>
+      </c>
       <c r="Z155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
@@ -13962,6 +14032,11 @@
           <t>CH</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
+        </is>
+      </c>
       <c r="Z156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
@@ -14014,6 +14089,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
+        </is>
+      </c>
       <c r="Z157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
@@ -14071,6 +14151,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>42ce7230-87bf-452a-b714-833a0716e519</t>
+        </is>
+      </c>
       <c r="Z158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
@@ -14133,6 +14218,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
+        </is>
+      </c>
       <c r="Z159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
@@ -14185,6 +14275,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
+        </is>
+      </c>
       <c r="Z160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
@@ -14242,6 +14337,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
+        </is>
+      </c>
       <c r="Z161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
@@ -14299,6 +14399,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
+        </is>
+      </c>
       <c r="Z162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
@@ -14356,6 +14461,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>f956b41d-482e-44be-a215-575d5455d551</t>
+        </is>
+      </c>
       <c r="Z163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
@@ -14413,6 +14523,11 @@
           <t>Front</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>55a9a5db-779c-4431-878f-621fd1035127</t>
+        </is>
+      </c>
       <c r="Z164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
@@ -14465,6 +14580,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
@@ -14522,6 +14642,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
+        </is>
+      </c>
       <c r="Z166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
@@ -14579,6 +14704,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
+        </is>
+      </c>
       <c r="Z167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
@@ -14636,6 +14766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>55349cf9-9743-4042-9932-3196803d0f29</t>
+        </is>
+      </c>
       <c r="Z168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
@@ -14693,6 +14828,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
+        </is>
+      </c>
       <c r="Z169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
@@ -14748,6 +14888,11 @@
       <c r="U170" t="inlineStr">
         <is>
           <t>1+2</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
@@ -14952,6 +15097,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
+        </is>
+      </c>
       <c r="Z174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
@@ -14999,6 +15149,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
+        </is>
+      </c>
       <c r="Z175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
@@ -15046,6 +15201,11 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
+        </is>
+      </c>
       <c r="Z176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
@@ -15093,6 +15253,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
+        </is>
+      </c>
       <c r="Z177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
@@ -15140,6 +15305,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
+        </is>
+      </c>
       <c r="Z178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
@@ -15187,6 +15357,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
+        </is>
+      </c>
       <c r="Z179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
@@ -15234,6 +15409,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
+        </is>
+      </c>
       <c r="Z180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
@@ -15281,6 +15461,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
+        </is>
+      </c>
       <c r="Z181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
@@ -15328,6 +15513,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
@@ -15380,6 +15570,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>f37af239-8d33-4787-93e6-4352245294b9</t>
+        </is>
+      </c>
       <c r="Z183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
@@ -15432,6 +15627,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
+        </is>
+      </c>
       <c r="Z184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
@@ -15482,6 +15682,11 @@
       <c r="S185" t="inlineStr">
         <is>
           <t>hhhhhllmlm</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
